--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ24"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2894,10 +2894,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131334799</v>
+        <v>136706855</v>
       </c>
       <c r="B21" t="n">
-        <v>57144</v>
+        <v>57184</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2905,16 +2905,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2943,10 +2943,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>477212</v>
+        <v>477252</v>
       </c>
       <c r="R21" t="n">
-        <v>6592292</v>
+        <v>6592364</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2973,27 +2973,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Grop i snötäcket.</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3019,33 +3014,33 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131334799</t>
+          <t>https://artportalen.se/Sighting/136706855</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130307942</v>
+        <v>131334799</v>
       </c>
       <c r="B22" t="n">
-        <v>57785</v>
+        <v>57144</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102622</v>
+        <v>102613</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Pärluggla</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Aegolius funereus</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3063,23 +3058,21 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Vrm</t>
+          <t>Lobergshöjden, Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>477219</v>
+        <v>477212</v>
       </c>
       <c r="R22" t="n">
-        <v>6592318</v>
+        <v>6592292</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3106,27 +3099,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2026-02-28</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:51</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Kontakläte hona.</t>
+          <t>Grop i snötäcket.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3152,60 +3145,67 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130307942</t>
+          <t>https://artportalen.se/Sighting/131334799</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127700271</v>
+        <v>130307942</v>
       </c>
       <c r="B23" t="n">
-        <v>58114</v>
+        <v>57785</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>102622</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Pärluggla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Aegolius funereus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Märrsprängaren, Märrsprängaren, Vrm</t>
+          <t>Lobergshöjden, Vrm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>477083</v>
+        <v>477219</v>
       </c>
       <c r="R23" t="n">
-        <v>6592331</v>
+        <v>6592318</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3232,27 +3232,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>I sumpskogskant.</t>
+          <t>Kontakläte hona.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3278,13 +3278,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127700271</t>
+          <t>https://artportalen.se/Sighting/130307942</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129482751</v>
+        <v>127700271</v>
       </c>
       <c r="B24" t="n">
         <v>58114</v>
@@ -3314,35 +3314,24 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>i par</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lobergshöjden, Vrm</t>
+          <t>Märrsprängaren, Märrsprängaren, Vrm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>477237</v>
+        <v>477083</v>
       </c>
       <c r="R24" t="n">
-        <v>6592311</v>
+        <v>6592331</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3369,27 +3358,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Med andra mesar.</t>
+          <t>I sumpskogskant.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3414,6 +3403,143 @@
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127700271</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129482751</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lobergshöjden, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>477237</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6592311</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Med andra mesar.</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jim Hellquist</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129482751</t>
         </is>
@@ -3444,6 +3570,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -2897,7 +2897,7 @@
         <v>136706855</v>
       </c>
       <c r="B21" t="n">
-        <v>57184</v>
+        <v>57186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -2897,7 +2897,7 @@
         <v>136706855</v>
       </c>
       <c r="B21" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -2897,7 +2897,7 @@
         <v>136706855</v>
       </c>
       <c r="B21" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -2927,16 +2927,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lobergshöjden, Lobergshöjden, Vrm</t>

--- a/artfynd/A 59523-2025 artfynd.xlsx
+++ b/artfynd/A 59523-2025 artfynd.xlsx
@@ -2897,7 +2897,7 @@
         <v>136706855</v>
       </c>
       <c r="B21" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
